--- a/src/attributions/attributions_ig_traj_483.xlsx
+++ b/src/attributions/attributions_ig_traj_483.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG5"/>
+  <dimension ref="A1:GG11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,28 +999,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6145147939207702</v>
+        <v>0.2090428975273069</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.03361328134365093</v>
+        <v>-0.04923131644705192</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0500535728619811</v>
+        <v>-0.01829204063419588</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1029,97 +1029,97 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1097214963802267</v>
+        <v>0.05823584854252709</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1511129680181663</v>
+        <v>0.09535033689852902</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.01520449914155581</v>
+        <v>-0.006951859529097442</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2402756913076364</v>
+        <v>0.07956457315260242</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.02197396897185276</v>
+        <v>0.00997581664425925</v>
       </c>
       <c r="W2" t="n">
-        <v>0.20487187360048</v>
+        <v>0.01490895479345783</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>-0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1754039755792008</v>
+        <v>0.07878910076441048</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.04522293598290503</v>
+        <v>-0.09763926908240748</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.00307570745556328</v>
+        <v>0.0803696368298539</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.05938161399306534</v>
+        <v>0.1014434240680914</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.1295114321085354</v>
+        <v>-0.03623813537214596</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.2156073006030146</v>
+        <v>0.1200799782548679</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
@@ -1128,28 +1128,28 @@
         <v>-0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT2" t="n">
         <v>-0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.8652138464551425</v>
+        <v>0.2813125494959109</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.1242123412251795</v>
+        <v>-0.0931230781870178</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.3388999303471824</v>
+        <v>-0.05270567445375807</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -1161,25 +1161,25 @@
         <v>-0</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.09823573342665089</v>
+        <v>-0.01956166164498817</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.0771579230489351</v>
+        <v>-0.009622078378804255</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.03673687846909692</v>
+        <v>-0.03059494986108409</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ2" t="n">
         <v>0</v>
@@ -1191,16 +1191,16 @@
         <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.2007303460526937</v>
+        <v>-0.07969365520839092</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.05010887092930697</v>
+        <v>0.02981723028141514</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.381407233797629</v>
+        <v>0.09454283435025368</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
@@ -1218,43 +1218,43 @@
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.445104766229371</v>
+        <v>0.1714341605679134</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.0297720278968848</v>
+        <v>-0.02562436580277574</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.2191595502210656</v>
+        <v>0.01656673125013242</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD2" t="n">
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.2465641217578499</v>
+        <v>-0.1630023116828898</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.0008182475690210679</v>
+        <v>0.1017636950380285</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.04424358405772369</v>
+        <v>-0.006476989996154158</v>
       </c>
       <c r="CI2" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL2" t="n">
         <v>-0</v>
@@ -1272,49 +1272,49 @@
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.2329361853514532</v>
+        <v>-0.11649448279125</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.1606681567538362</v>
+        <v>0.1378687162796585</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.5101448846631088</v>
+        <v>-0.01005643693647668</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
         <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.2401629246447005</v>
+        <v>-0.1627958174992551</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.02033394049873151</v>
+        <v>0.08871393034063703</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.0212670998604758</v>
+        <v>-0.0005791043191160887</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
         <v>0</v>
@@ -1326,46 +1326,46 @@
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.1689092553282468</v>
+        <v>-0.02622268426018215</v>
       </c>
       <c r="DG2" t="n">
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.05569784736116114</v>
+        <v>0.02068458365316585</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.07527890748325758</v>
+        <v>-0.09539955515693485</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN2" t="n">
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.2860681481145561</v>
+        <v>-0.1089132585398691</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0.1263664946653228</v>
+        <v>0.04554224001408882</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.161459935618606</v>
+        <v>-0.0159245044030188</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
         <v>-0</v>
@@ -1377,19 +1377,19 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.3410344511273106</v>
+        <v>-0.06132210793422019</v>
       </c>
       <c r="DY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.159137581411516</v>
+        <v>-0.04409047199421198</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.1028234934840929</v>
+        <v>-0.005113945913941214</v>
       </c>
       <c r="EB2" t="n">
         <v>0</v>
@@ -1401,31 +1401,31 @@
         <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF2" t="n">
         <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.1920428433723034</v>
+        <v>-0.1546849578431237</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.02742670378936055</v>
+        <v>0.1235388946294841</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.1145181190926399</v>
+        <v>0.01817511758913084</v>
       </c>
       <c r="EK2" t="n">
         <v>0</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN2" t="n">
         <v>-0</v>
@@ -1434,22 +1434,22 @@
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.0354527403160796</v>
+        <v>0.05560128558834698</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.04052806088710589</v>
+        <v>0.01818672183220707</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.2380808607003599</v>
+        <v>0.01876978108747007</v>
       </c>
       <c r="ET2" t="n">
         <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
         <v>-0</v>
@@ -1461,19 +1461,19 @@
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.2451725819939197</v>
+        <v>-0.1743316478427678</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.007653701871588447</v>
+        <v>0.1054071820558904</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.001855340382163905</v>
+        <v>-0.02577335345186668</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
         <v>0</v>
@@ -1485,46 +1485,46 @@
         <v>-0</v>
       </c>
       <c r="FG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.09305720607776297</v>
+        <v>-0.0564619988768561</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.02749367261714162</v>
+        <v>0.04780273847462701</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.2286587942541162</v>
+        <v>-0.05883320879040702</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP2" t="n">
         <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.0694090615856245</v>
+        <v>-0.1758534447121212</v>
       </c>
       <c r="FR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.08951722321098526</v>
+        <v>0.0428106603722972</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.1018271964832186</v>
+        <v>0.09832376029736763</v>
       </c>
       <c r="FU2" t="n">
         <v>-0</v>
@@ -1533,34 +1533,34 @@
         <v>0</v>
       </c>
       <c r="FW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX2" t="n">
         <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.1467816729748712</v>
+        <v>-0.1637203455080085</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>-0.05709298077279943</v>
+        <v>0.0690630691793797</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
         <v>-0</v>
       </c>
       <c r="GE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG2" t="n">
         <v>-0</v>
@@ -1571,7 +1571,7 @@
         <v>-0</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -1580,76 +1580,76 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02299752750445317</v>
+        <v>-0.02274864350811157</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1437686821525809</v>
+        <v>0.02226543062044707</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01452278463044653</v>
+        <v>-0.1082795218075874</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0121571063521048</v>
+        <v>-0.01302839547273572</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.02973471611699382</v>
+        <v>0.01588557929498344</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00596967444231853</v>
+        <v>-0.02965802609410391</v>
       </c>
       <c r="S3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.001623927424013259</v>
+        <v>-0.1291347226019817</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.08968712158189632</v>
+        <v>-0.1233980783149781</v>
       </c>
       <c r="Y3" t="n">
         <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.01559044688913006</v>
+        <v>0.0007086709381776869</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC3" t="n">
         <v>-0</v>
@@ -1661,19 +1661,19 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.002680778325834483</v>
+        <v>0.01739921425209554</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.0520393557716593</v>
+        <v>-0.1047205695166557</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.01120939101392627</v>
+        <v>0.005837550409436432</v>
       </c>
       <c r="AK3" t="n">
         <v>-0</v>
@@ -1682,16 +1682,16 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.03653479877975602</v>
+        <v>0.07270444170590709</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.01800063227981107</v>
+        <v>-0.04050328671431205</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -1700,13 +1700,13 @@
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0111132904284128</v>
+        <v>-0.05183889774022092</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV3" t="n">
         <v>-0</v>
@@ -1715,106 +1715,106 @@
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.01504759253069165</v>
+        <v>-0.01809492811283318</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.056691040538385</v>
+        <v>-0.05357911933068305</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.005704399345973567</v>
+        <v>-0.07070935261119425</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.01756609270986396</v>
+        <v>-0.004762698677789533</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.06491054404638923</v>
+        <v>-0.04757304581153796</v>
       </c>
       <c r="BI3" t="n">
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.003922139348404579</v>
+        <v>-0.01829685424018923</v>
       </c>
       <c r="BL3" t="n">
         <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
         <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.03971742396950115</v>
+        <v>0.08147054344222616</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0.004032304894061108</v>
+        <v>-0.003639712154852601</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.0202478132668822</v>
+        <v>0.05899323303081901</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW3" t="n">
         <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.01055497296772735</v>
+        <v>-0.05910377983337104</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.08248186782063273</v>
+        <v>-0.1087551018977317</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.006905082138520148</v>
+        <v>-0.07264347982162959</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF3" t="n">
         <v>0</v>
@@ -1823,64 +1823,64 @@
         <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.004426778255723996</v>
+        <v>0.01123541493220276</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.04011709781561153</v>
+        <v>0.002908014551553773</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
         <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.002193612287067432</v>
+        <v>0.03341964574493228</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP3" t="n">
         <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.02280188752488282</v>
+        <v>-0.07380090256177223</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.01911402659249005</v>
+        <v>0.2571323825751934</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.02721114759792663</v>
+        <v>0.001855765894891027</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.01302154149826043</v>
+        <v>0.004716228727866464</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.03499406591624343</v>
+        <v>0.009179544001091505</v>
       </c>
       <c r="DB3" t="n">
         <v>-0</v>
@@ -1889,7 +1889,7 @@
         <v>-0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.005017043947803913</v>
+        <v>0.04115143122175416</v>
       </c>
       <c r="DE3" t="n">
         <v>-0</v>
@@ -1901,67 +1901,67 @@
         <v>-0</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.008858154188820688</v>
+        <v>-0.02677918910227048</v>
       </c>
       <c r="DJ3" t="n">
-        <v>9.990033694249219e-05</v>
+        <v>0.008828493879301888</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0.00270900010134948</v>
+        <v>0.02936516189888804</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.0530265085263922</v>
+        <v>0.006256212829226909</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.002380977462496033</v>
+        <v>-0.01909277999607004</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU3" t="n">
         <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.009177652131066428</v>
+        <v>-0.03045218398549882</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.001109513777695862</v>
+        <v>-0.03792772076276901</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.05259828832060618</v>
+        <v>-0.03946662201910703</v>
       </c>
       <c r="EC3" t="n">
         <v>-0</v>
@@ -1970,10 +1970,10 @@
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.002307866571176197</v>
+        <v>0.03593074031965834</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG3" t="n">
         <v>0</v>
@@ -1985,37 +1985,37 @@
         <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.01246122423842875</v>
+        <v>0.03210505966725508</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.04579727341377277</v>
+        <v>0.01554728666170764</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN3" t="n">
-        <v>-0.01811137862338874</v>
+        <v>0.04956677696358312</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP3" t="n">
         <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.07153053756579819</v>
+        <v>-0.05341462498834507</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.02157414629998418</v>
+        <v>0.03629245285138689</v>
       </c>
       <c r="EU3" t="n">
         <v>0</v>
@@ -2024,25 +2024,25 @@
         <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0.007984842117833492</v>
+        <v>0.04610909868402067</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA3" t="n">
         <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.02301521441416165</v>
+        <v>-0.009767630018435999</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.03503251009807778</v>
+        <v>-0.004592172940225988</v>
       </c>
       <c r="FD3" t="n">
         <v>0</v>
@@ -2051,67 +2051,67 @@
         <v>0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.007184397511117065</v>
+        <v>0.04510135933057283</v>
       </c>
       <c r="FG3" t="n">
         <v>-0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI3" t="n">
         <v>0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.06434730891474054</v>
+        <v>-0.01087260738770988</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.02123203687618649</v>
+        <v>-0.02351069229223852</v>
       </c>
       <c r="FM3" t="n">
         <v>-0</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.0320724071391601</v>
+        <v>0.0753756576239067</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ3" t="n">
         <v>0</v>
       </c>
       <c r="FR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.04887372710772088</v>
+        <v>-0.04128085129633125</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.01051348668726339</v>
+        <v>0.137720228203286</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW3" t="n">
         <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>-0.02809275625361709</v>
+        <v>0.1378244936560251</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA3" t="n">
         <v>-0</v>
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.01617178544562238</v>
+        <v>0.02592538385091482</v>
       </c>
       <c r="GE3" t="n">
         <v>-0</v>
@@ -2132,108 +2132,108 @@
         <v>-0</v>
       </c>
       <c r="GG3" t="n">
-        <v>-0.01468179471608425</v>
+        <v>0.007917769640839472</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.1478106215635777</v>
+        <v>0.1587361868943276</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2927859725821418</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02452625868369276</v>
+        <v>0.069810336366537</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>-0.120932664675829</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.04764918353724493</v>
+        <v>0.0573132525062651</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2621506481273062</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01592162054899619</v>
+        <v>-0.006417814546464083</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>-0.04265031318671293</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>-0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1174052789888454</v>
+        <v>0.02955080944815561</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00229017273453419</v>
+        <v>-0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.02034863890473155</v>
+        <v>-0.03147482824443494</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.01427217197686494</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" t="n">
         <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.07535838085802857</v>
+        <v>-0.02669913185382276</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.0004324252840452669</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.007430165632723951</v>
+        <v>-0.02136011637327411</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0</v>
+        <v>-0.05152028982784649</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -2242,25 +2242,25 @@
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK4" t="n">
         <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.0606492425612185</v>
+        <v>0.03961931641237385</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.03413351815417421</v>
+        <v>-0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.08245799530903208</v>
+        <v>0.05241071515769773</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0</v>
+        <v>-0.04800052071026042</v>
       </c>
       <c r="AQ4" t="n">
         <v>0</v>
@@ -2269,85 +2269,85 @@
         <v>-0</v>
       </c>
       <c r="AS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.149407547529197</v>
+        <v>0.1225178057443483</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.1158006467842088</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.01254403888257485</v>
+        <v>-0.07816099811058923</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>-0.1298964300005214</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.02453935840385798</v>
+        <v>-0.01473420321445322</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.09280069781651246</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.04921282121720424</v>
+        <v>0.05688049338486705</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>-0.01793054557011803</v>
       </c>
       <c r="BI4" t="n">
         <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.04484253896021193</v>
+        <v>-0.03826821278575662</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0.04053348234336743</v>
+        <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.07836174272364263</v>
+        <v>0.0268889753956609</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>0.03116950981073067</v>
       </c>
       <c r="BR4" t="n">
         <v>-0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
         <v>0</v>
@@ -2356,79 +2356,79 @@
         <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>-0.05502219111593847</v>
+        <v>0.09486922672469265</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0264978768838823</v>
+        <v>-0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.02531704175666252</v>
+        <v>-0.02072401339935892</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>-0.07091944163143933</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.03597797839531857</v>
+        <v>-0.05848930017622598</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>-0.04936029297263095</v>
+        <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.01873767972091876</v>
+        <v>-0.01579565716112898</v>
       </c>
       <c r="CI4" t="n">
-        <v>0</v>
+        <v>0.05604533713709977</v>
       </c>
       <c r="CJ4" t="n">
         <v>-0</v>
       </c>
       <c r="CK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.02537219207168184</v>
+        <v>0.006983262136612139</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.02767287830194433</v>
+        <v>0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.07357728225080101</v>
+        <v>0.01493704385544392</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0</v>
+        <v>0.05295010658232631</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU4" t="n">
         <v>-0</v>
@@ -2437,49 +2437,49 @@
         <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.050989364040695</v>
+        <v>-0.068854128761472</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>-0.05357870182052617</v>
+        <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.01248575984578124</v>
+        <v>-0.01184799401474924</v>
       </c>
       <c r="DA4" t="n">
-        <v>-0</v>
+        <v>0.07159221113572585</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD4" t="n">
         <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.03193534587914142</v>
+        <v>0.1254544773050226</v>
       </c>
       <c r="DG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.01114762552349051</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.08391625223303409</v>
+        <v>0.0003122574052105829</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0</v>
+        <v>0.02914533247516236</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>-0</v>
@@ -2491,22 +2491,22 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.03608046185740413</v>
+        <v>-0.03380848476257867</v>
       </c>
       <c r="DP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.04600104413906536</v>
+        <v>-0</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.05404310148827565</v>
+        <v>0.0704322202605657</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0</v>
+        <v>0.07078473243818348</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>-0</v>
@@ -2518,25 +2518,25 @@
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.05221084938934404</v>
+        <v>-0.02652085765717334</v>
       </c>
       <c r="DY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.02787387099698214</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.07044096955745288</v>
+        <v>0.06180482088894538</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>0.07850093772241676</v>
       </c>
       <c r="EC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE4" t="n">
         <v>-0</v>
@@ -2545,46 +2545,46 @@
         <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0428160241528717</v>
+        <v>0.005889182739533578</v>
       </c>
       <c r="EH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.09640771299951979</v>
+        <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.02473010648522069</v>
+        <v>-0.03481520289028314</v>
       </c>
       <c r="EK4" t="n">
-        <v>-0</v>
+        <v>0.009719397972722867</v>
       </c>
       <c r="EL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.05409080100757386</v>
+        <v>-0.09175289030899497</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.04919256369738638</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.02521287167988731</v>
+        <v>0.007655499775058775</v>
       </c>
       <c r="ET4" t="n">
-        <v>0</v>
+        <v>0.007915792812304584</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
@@ -2593,31 +2593,31 @@
         <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.04897473830685852</v>
+        <v>-0.06165178195980377</v>
       </c>
       <c r="EZ4" t="n">
         <v>0</v>
       </c>
       <c r="FA4" t="n">
-        <v>-0.04149633836636276</v>
+        <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.02041109822417571</v>
+        <v>-0.02622489239659611</v>
       </c>
       <c r="FC4" t="n">
-        <v>0</v>
+        <v>0.05611060090770466</v>
       </c>
       <c r="FD4" t="n">
         <v>-0</v>
       </c>
       <c r="FE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF4" t="n">
         <v>-0</v>
@@ -2626,79 +2626,79 @@
         <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.02040993664052513</v>
+        <v>-0.02633673672723611</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>-0.009614804732790463</v>
+        <v>0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.005482352323478792</v>
+        <v>-0.002605116625087168</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0.03317846423041811</v>
       </c>
       <c r="FM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN4" t="n">
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.007613442978717311</v>
+        <v>-0.03687417094609339</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>-0.004361956712463476</v>
+        <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.01022379561184541</v>
+        <v>-0.02866911843012004</v>
       </c>
       <c r="FU4" t="n">
-        <v>0</v>
+        <v>-0.03337310992960645</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY4" t="n">
         <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.05749795670634561</v>
+        <v>-0.06056154354690108</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.03091515141879977</v>
+        <v>-0</v>
       </c>
       <c r="GC4" t="n">
         <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>0</v>
+        <v>0.01704334875335267</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG4" t="n">
         <v>0</v>
@@ -2706,79 +2706,79 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>0.1024377047309716</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0.1624599908244033</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0</v>
+        <v>0.0356503275672563</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.03944862868539177</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.114638090915634</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0</v>
+        <v>-0.01119936849672283</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.05586398693336254</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.04689346685037113</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0</v>
+        <v>0.219316917076826</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -2787,160 +2787,160 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-0.02538244301792594</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-0.1440206557856344</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0</v>
+        <v>0.06464792140596025</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>0.05819654417539612</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0.07433543699062449</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0</v>
+        <v>0.137455285799732</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>0.07849432911743268</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>-0.05601984715829526</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0</v>
+        <v>0.05870621516972469</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-0.003572040629825224</v>
       </c>
       <c r="BD5" t="n">
         <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>-0.1156464027765609</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0</v>
+        <v>-0.09490700107709028</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>-0.06866565902127465</v>
       </c>
       <c r="BM5" t="n">
         <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>0.03181184602337197</v>
       </c>
       <c r="BO5" t="n">
         <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0</v>
+        <v>-0.00627080456963152</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS5" t="n">
         <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>0.0889908275927678</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0.05463351350484897</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0</v>
+        <v>0.04688735806164314</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
@@ -2949,73 +2949,73 @@
         <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0.02922111954191705</v>
       </c>
       <c r="CE5" t="n">
         <v>0</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>0.08821230196629319</v>
       </c>
       <c r="CG5" t="n">
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0</v>
+        <v>-0.03554809672605369</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>-0.01504473392222039</v>
       </c>
       <c r="CN5" t="n">
         <v>0</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>0.02726701536621963</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0</v>
+        <v>0.1804292950932463</v>
       </c>
       <c r="CR5" t="n">
         <v>0</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0.03292404187174718</v>
       </c>
       <c r="CW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX5" t="n">
-        <v>0</v>
+        <v>0.07095758570058532</v>
       </c>
       <c r="CY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0</v>
+        <v>-0.0183056067586381</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
@@ -3030,22 +3030,22 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>-0.01417239860909667</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>0.002952102745476646</v>
       </c>
       <c r="DH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0</v>
+        <v>-0.07950844858373492</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
@@ -3054,205 +3054,205 @@
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0.0009843818362752662</v>
       </c>
       <c r="DO5" t="n">
         <v>0</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>0.07661175906530809</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0</v>
+        <v>-0.09795878345544094</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>0.01618158681121613</v>
       </c>
       <c r="DX5" t="n">
         <v>0</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>0.152167101072793</v>
       </c>
       <c r="DZ5" t="n">
         <v>0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0</v>
+        <v>0.1183356693541038</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
         <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0.008124358207717969</v>
       </c>
       <c r="EG5" t="n">
         <v>0</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>0.03575206895976697</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0</v>
+        <v>-0.01468132408391051</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0.06926069879291347</v>
       </c>
       <c r="EP5" t="n">
         <v>0</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>0.04678469017973189</v>
       </c>
       <c r="ER5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0</v>
+        <v>-0.0255718538625568</v>
       </c>
       <c r="ET5" t="n">
         <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0.0273354251702384</v>
       </c>
       <c r="EY5" t="n">
         <v>0</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>0.05768765594954336</v>
       </c>
       <c r="FA5" t="n">
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0</v>
+        <v>-0.004434296907809085</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>0.02252103729781318</v>
       </c>
       <c r="FH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>0.03174445677716286</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0</v>
+        <v>-0.1123610845778763</v>
       </c>
       <c r="FL5" t="n">
         <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN5" t="n">
         <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0.01362538627636689</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>0.08549692834454563</v>
       </c>
       <c r="FS5" t="n">
         <v>0</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0</v>
+        <v>-0.08446074290028448</v>
       </c>
       <c r="FU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV5" t="n">
         <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>0</v>
+        <v>-0.04123359289834798</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA5" t="n">
-        <v>0</v>
+        <v>0.009090538979980941</v>
       </c>
       <c r="GB5" t="n">
         <v>0</v>
@@ -3267,10 +3267,3424 @@
         <v>0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
-        <v>0</v>
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.413310445186738</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.1326123787497007</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.01139681379781842</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.04433073932798415</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.370755388287634</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.1784937549767011</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.05341578385849869</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.005372437819512224</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.06956867719937851</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.06309567794749761</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.06843076176867591</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.02855202374865368</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.03474007959392741</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-0.1713887232510318</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.1165089034655008</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.01332611628123527</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1425869039182324</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.0341879953011158</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.04166707693153181</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.1085361818511415</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.3116136825815031</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-0.003067684028995638</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0.1423472500125996</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0.01184311650308882</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0.02378577083542622</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-0.109998355807814</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0.06352815568597525</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-0.02144383765533928</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.03710871591177822</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.02926703743396649</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.1073356884143271</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.02625533541796547</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.2373449743652682</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>-0.05370838909452618</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-0.02870575016993748</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>-0.02743942566080944</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0.131439350360972</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.05933120818728004</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.01049052198520504</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.01645338844169177</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>-0.07671393836366225</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0.1052595799563681</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.1078657415389859</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.04746600657889922</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>-0.1134903197454643</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0.05075253433312771</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0.01076958974086237</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.014926169337568</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0.01009838278603015</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0.01090141340430771</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0.2186431338686165</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0.01132003740524527</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0.09150173409174155</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>-0.003999810019253631</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>-0.04761705435954106</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.01625442891195637</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0.03821527043822127</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0.01634784149805794</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>-0.05785810362278153</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>-0.08761547418989044</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>-0.05649920783126463</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0.07915299492706365</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>0.01718683735996371</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0.004915079935566199</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>-0.06980711471516653</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>-0.009193119441273686</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>-0.02775130430767366</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0.09420799067431898</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>-0.1389975989999372</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0.05127033634921201</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>-0.004392933970873033</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0.002771012251356059</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>-0.05524553360004462</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0.07745611418101138</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>-0.02808700915207489</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0.09472052002199545</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>-0.123413172207004</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0.1915492146373692</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0.008629543808728568</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0.006238879851779755</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>-0.09802823023108909</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>-0.02636349285800007</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>-0.01129774200680828</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.3933721644531456</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.02841367895312679</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3701302685515935</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.2612463268709806</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.08086883094779802</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.2542369659003711</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.1156902989104685</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.01927454569483026</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.03266786321545674</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.02740003972135142</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.2076647049995671</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.02114762251600576</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-0.1432904673678508</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-0.1072686008621392</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.1599197399093172</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-0.3083609988162314</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.07012099118243763</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.1318725776802699</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.1035950543326565</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.2054091954963481</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.152661866491136</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-0.01665159559637816</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>-0.08895587384351009</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>-0.04029172576551594</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>-0.3028334106857457</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-0.02408065916226686</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.1108870194184877</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.1334434545806708</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.003585769559030238</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>-0.08358850206028662</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.1247881619448478</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>-0.1901972162733653</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>-0.03791813673852203</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0.1241989594313406</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>-0.005207477729462446</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>-0.09662330953602603</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>-0.004558467392882767</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.08595001965342446</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>-0.03556873539150514</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0.02245386238375076</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.06762619244240486</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>-0.01702958821283192</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>-0.03720395274385337</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.02975250619648735</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0.02619639179340464</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0.07140182957495753</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>-0.005159234526135629</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.01082704887932697</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>0.1473888575234427</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>0.07628671837997356</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.1321510877699903</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>0.1512402893293635</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>0.02284389765973495</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>-0.07633664777354518</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>0.1227417446422056</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>-0.04693377558984834</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>-0.1456903284861093</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.1313906954497938</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>-0.02390097457660706</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>-0.05219992376709102</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>0.1403456158459309</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0.02765427953627419</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.2733550750099168</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.009864694095000844</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2535487927211952</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.2637212254745886</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.1241146988715049</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.1773135201792092</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.06238617996555054</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.02114679721595961</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.1060221353093043</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.04837139179199056</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.03091603615180989</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.002170384612791257</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0.1154674774305041</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0.1726383865038935</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.07844517207008399</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-0.1765070920869149</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0.07023050091158346</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.2432143704749381</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.1465035862003831</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.09648143151026969</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.008536174337299519</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.05554186269929005</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>-0.04291027266092027</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0.004542215596851086</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-0.1391143649044655</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0.05170551333116567</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0.2095384037407868</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0.1499628046811615</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.001236067127236478</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>-0.07974188002622801</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0.08101884313531256</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>-0.06466613991606877</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>-0.1820959310526777</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0.1581726499121453</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>-0.0271539809208515</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>-0.08899276426393307</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-0.009721253276974961</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-0.0108316191897667</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>-0.06966350831058682</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>0.0440343144375796</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0.02365149691656627</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>-0.05656195358542299</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0.09842958746466243</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0.02216603618754906</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0.1456227046093964</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>0.1430122816709468</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>-0.03302681036245957</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0.01108666862892805</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>-0.07151139732696327</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>0.02222163107785351</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>-0.00344278532635093</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>0.1681653888667807</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>0.0008633542603493397</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>-0.09898157121265468</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>0.07086005153885684</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0.02353262750393826</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>-0.03133727968154899</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0.1486924847234183</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>0.04012940014415473</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0.01230049161884712</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0.1689519148526515</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>-0.0156769015575546</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.2197557248509211</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1066713463279709</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3983834283034816</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.1528643329578764</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.2514350149370714</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.3808701025543822</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.08734309789915105</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.1329446236161325</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.04337269475453008</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.07101654870315173</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.1647294359829512</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.09750623332627564</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.1288433082802226</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-0.05376897522193432</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.09381138218393453</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0.2982957206087531</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.127208159330942</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.1933624462656853</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.06221135584763918</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.1330728607114275</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.1185415484584729</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>-0.01895997216580859</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-0.1002699335645769</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-0.0110226881441917</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>-0.1879711102592198</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.09662939650983902</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.1609330460301004</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.102601874479768</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>-0.02960862467092536</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>-0.0991410190788502</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.1389004278471621</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>-0.1677770990256953</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-0.1010533891016032</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.07934966937338855</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>-0.04669284670783497</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>-0.1090625549304068</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0.04598244406638222</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.08956509196190773</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-0.02948536513285952</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>-0.03091245454838908</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0.1038103362888695</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>-0.03473022457320381</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>-0.1010101372924306</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.02960554789758222</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>-0.02648466611442384</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.05928177037953343</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>-0.039696418038795</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>-0.02189140424462118</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.04523526146586167</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>-0.03007114163212363</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>-0.1509651398549153</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.1118036741904451</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>-0.0202907491345175</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>-0.1019110598334981</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.09605340694557529</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>-0.04877242445492353</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>-0.1276065439490078</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>-0.01269840848594906</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>0.01314886787442708</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>-0.06269249608523335</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.06365421323372594</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.01663887204486683</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
